--- a/benchmark/generated_files/CC-2_V_048.xlsx
+++ b/benchmark/generated_files/CC-2_V_048.xlsx
@@ -472,18 +472,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211987312 ORD. EPSILON DIGITAL SRL</t>
+          <t>Addebito SDD - JETBRAINS S.R.O. INTELLIJ IDEA</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1951.06</v>
+        <v>-130.66</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -493,18 +493,18 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216111775 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:216127322 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3005.49</v>
+        <v>3906.03</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -514,18 +514,18 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211811188 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:217402195 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5201.44</v>
+        <v>4632.19</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -535,18 +535,18 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210237208 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:210104637 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3337.72</v>
+        <v>1604.22</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -556,18 +556,18 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214316391 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:213420709 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3867.68</v>
+        <v>5360.76</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -577,18 +577,18 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>46031</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>46032</v>
-      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212716817 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:215079081 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4685.85</v>
+        <v>5427.98</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -598,18 +598,18 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46035</v>
+        <v>46031</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219504599 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:210936819 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4898.35</v>
+        <v>2123.05</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -626,11 +626,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212383525 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:215159644 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2959.36</v>
+        <v>4793.37</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -640,18 +640,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215225526 ORD. ROSSI MARCO GIROCONTO</t>
+          <t>GIROCONTO DA CC 0075849 A CC 0123456</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-705.4</v>
+        <v>-857.73</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -661,18 +661,18 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211042209 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:216424762 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1757.42</v>
+        <v>3805.27</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -682,18 +682,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46049</v>
+        <v>46043</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46050</v>
+        <v>46044</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218788838 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:210880248 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3558.78</v>
+        <v>4780.15</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -703,18 +703,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215190801 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:212356101 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4446.36</v>
+        <v>5488.9</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -724,18 +724,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46052</v>
+        <v>46050</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216130822 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:213175169 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4055.32</v>
+        <v>2738.44</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -745,18 +745,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46054</v>
+        <v>46051</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46054</v>
+        <v>46051</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211593349 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:219216854 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4726.81</v>
+        <v>2584.1</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -766,18 +766,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46060</v>
+        <v>46052</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217385086 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:218934490 ORD. ROSSI MARCO GIROCONTO</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4455.64</v>
+        <v>-600.59</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -787,18 +787,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46060</v>
+        <v>46055</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46060</v>
+        <v>46055</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215702020 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:217614882 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3672.8</v>
+        <v>4547.76</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -808,18 +808,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46061</v>
+        <v>46058</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46061</v>
+        <v>46058</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213709126 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:214942372 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5106.52</v>
+        <v>2299.32</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -829,18 +829,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214635900 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:213533419 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3511.76</v>
+        <v>2074.15</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46062</v>
+        <v>46060</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211898421 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:215136594 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2593.31</v>
+        <v>5418.98</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -871,18 +871,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218827228 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:217967236 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>3152.26</v>
+        <v>2075.56</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -892,18 +892,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>Bonif. v/fav. - RIF:212247271 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-137.14</v>
+        <v>3308.26</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -913,18 +913,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211770178 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:219545852 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2324.58</v>
+        <v>1567.49</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -934,18 +934,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46069</v>
+        <v>46065</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46070</v>
+        <v>46066</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211679821 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:219127262 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1620.27</v>
+        <v>284.46</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -955,18 +955,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46072</v>
+        <v>46068</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46072</v>
+        <v>46068</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:217151287 BEN. IDRAULICO ROSSI PAOLO</t>
+          <t>Bonif. v/fav. - RIF:212123127 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-60.16</v>
+        <v>2889.74</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -976,18 +976,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 105,43 EUR DEL 25.02.2026 A (ITA) UDEMY.COM FORMAZIONE</t>
+          <t>Bonif. v/fav. - RIF:219177944 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-105.43</v>
+        <v>425.41</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -997,18 +997,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217962034 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:219191262 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1704.45</v>
+        <v>2185.08</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1018,18 +1018,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46079</v>
+        <v>46069</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46079</v>
+        <v>46069</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>Pagam. POS - PAGAMENTO POS 31,69 EUR DEL 16.02.2026 A (ITA) BUFFETTI FLAMINIO</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-67.48</v>
+        <v>-31.69</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1039,18 +1039,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46080</v>
+        <v>46072</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46080</v>
+        <v>46072</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213608424 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:213378032 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5161.63</v>
+        <v>4659.47</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218342002 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>GIROCONTO DA CC 0075849 A CC 0123456</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4411.25</v>
+        <v>-642.37</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1081,18 +1081,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213277114 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:215256438 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2011.4</v>
+        <v>3478.14</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Saldo finale: 27.433,17 EUR</t>
+          <t>Saldo finale: 3.410,29 EUR</t>
         </is>
       </c>
     </row>
